--- a/tools/me-cleanup-import/projects-clean.xlsx
+++ b/tools/me-cleanup-import/projects-clean.xlsx
@@ -10328,7 +10328,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10564,9 +10564,165 @@
         <v>Redundant — use Skilled jobs (32) + Unskilled jobs (33)</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>16</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Number of Additional Classrooms</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Household sanitation connections (65)</v>
+      </c>
+      <c r="E10">
+        <v>16</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Misassigned — use Household sanitation connections (65) on AC16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>30</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Number of Capacity Development Plans</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Community development plans (10)</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Duplicate — use Community development plans (10) on AC10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>55</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Number of Market Sheds</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Markets and commercial facilities (19)</v>
+      </c>
+      <c r="E12">
+        <v>19</v>
+      </c>
+      <c r="F12">
+        <v>19</v>
+      </c>
+      <c r="G12" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Duplicate — use Markets and commercial facilities (19) on AC19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>58</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Number of Market Stalls</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Markets and commercial facilities (19)</v>
+      </c>
+      <c r="E13">
+        <v>19</v>
+      </c>
+      <c r="F13">
+        <v>19</v>
+      </c>
+      <c r="G13" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Duplicate — use Markets and commercial facilities (19) on AC19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>61</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Number of Storm Water Drains</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>Storm water drainage (23)</v>
+      </c>
+      <c r="E14">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>23</v>
+      </c>
+      <c r="G14" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Duplicate — use Storm water drainage (23) on AC23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>67</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Number of Vending platforms</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Markets and commercial facilities (19)</v>
+      </c>
+      <c r="E15">
+        <v>19</v>
+      </c>
+      <c r="F15">
+        <v>19</v>
+      </c>
+      <c r="G15" t="str">
+        <v>remove_on_import</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Duplicate — use Markets and commercial facilities (19) on AC19</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11589,7 +11745,7 @@
         <v>IND-AC36</v>
       </c>
       <c r="D8" t="str">
-        <v>CDPs implemented</v>
+        <v>CDP outputs</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -12437,7 +12593,7 @@
         <v>IND-AC-FURN</v>
       </c>
       <c r="D24" t="str">
-        <v>Furnished housing units</v>
+        <v>Housing unit furnishings</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -13020,7 +13176,7 @@
         <v>IND-AC-LAND</v>
       </c>
       <c r="D35" t="str">
-        <v>Land parcels acquired</v>
+        <v>Land parcels</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -13550,7 +13706,7 @@
         <v>IND06</v>
       </c>
       <c r="D45" t="str">
-        <v>Registry index maps (RIMs)</v>
+        <v>Registry index maps</v>
       </c>
       <c r="E45" t="str">
         <v>Number of Registry Index Maps (RIMs)</v>
@@ -14769,7 +14925,7 @@
         <v>IND11</v>
       </c>
       <c r="D68" t="str">
-        <v>Vulnerable persons identified</v>
+        <v>Vulnerable persons</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -40467,7 +40623,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="str">
-        <v>Amend registry index maps (RIMs)</v>
+        <v>Amend registry index maps</v>
       </c>
       <c r="C3" t="str">
         <v>RIM amendment</v>
@@ -40985,10 +41141,10 @@
         <v>Play Area</v>
       </c>
       <c r="H13" t="str">
-        <v>NITui9KKl</v>
+        <v>AC53</v>
       </c>
       <c r="I13" t="str">
-        <v>NITui9KKl</v>
+        <v>AC53</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -41017,7 +41173,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="str">
-        <v>Construct education facility blocks (classrooms, ablution and kitchen)</v>
+        <v>Construct education facility blocks</v>
       </c>
       <c r="C14" t="str">
         <v>Education facility construction</v>
@@ -41285,10 +41441,10 @@
         <v>Public Parks</v>
       </c>
       <c r="H19" t="str">
-        <v>4zXiYYv3p</v>
+        <v>AC50</v>
       </c>
       <c r="I19" t="str">
-        <v>4zXiYYv3p</v>
+        <v>AC50</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -41967,7 +42123,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="str">
-        <v>Implement digital public works (DPW)</v>
+        <v>Implement digital public works</v>
       </c>
       <c r="C33" t="str">
         <v>DPW implementation</v>
@@ -42017,7 +42173,7 @@
         <v>12</v>
       </c>
       <c r="B34" t="str">
-        <v>Implement labour-intensive civil works (LICW)</v>
+        <v>Implement labour-intensive civil works</v>
       </c>
       <c r="C34" t="str">
         <v>LICW implementation</v>
@@ -42135,10 +42291,10 @@
         <v>Dumpster</v>
       </c>
       <c r="H36" t="str">
-        <v>jF8Tdgbs8</v>
+        <v>AC51</v>
       </c>
       <c r="I36" t="str">
-        <v>jF8Tdgbs8</v>
+        <v>AC51</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -42167,7 +42323,7 @@
         <v>20</v>
       </c>
       <c r="B37" t="str">
-        <v>Install security and high-mast floodlights (including solar-powered)</v>
+        <v>Install security and high-mast floodlights</v>
       </c>
       <c r="C37" t="str">
         <v>Floodlight installation</v>
@@ -42667,7 +42823,7 @@
         <v>38</v>
       </c>
       <c r="B47" t="str">
-        <v>Prepare environmental and social impact assessment (ESIA) report</v>
+        <v>Prepare environmental and social impact assessment report</v>
       </c>
       <c r="C47" t="str">
         <v>ESIA preparation</v>
@@ -42717,7 +42873,7 @@
         <v/>
       </c>
       <c r="B48" t="str">
-        <v>Prepare environmental and social management plans (ESMPs)</v>
+        <v>Prepare environmental and social management plans</v>
       </c>
       <c r="C48" t="str">
         <v>ESMP preparation</v>
@@ -42817,7 +42973,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="str">
-        <v>Prepare local physical and land use development plans (LP&amp;LUDPs)</v>
+        <v>Prepare local physical and land use development plans</v>
       </c>
       <c r="C50" t="str">
         <v>LP&amp;LUDP preparation</v>
@@ -42867,7 +43023,7 @@
         <v/>
       </c>
       <c r="B51" t="str">
-        <v>Prepare resettlement action plans (RAPs)</v>
+        <v>Prepare resettlement action plans</v>
       </c>
       <c r="C51" t="str">
         <v>RAP preparation</v>
@@ -75132,7 +75288,7 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>CDPs implemented</v>
+        <v>CDP outputs</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -75927,7 +76083,7 @@
         <v/>
       </c>
       <c r="B23" t="str">
-        <v>Furnished housing units</v>
+        <v>Housing unit furnishings</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -76457,7 +76613,7 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>Land parcels acquired</v>
+        <v>Land parcels</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -76987,7 +77143,7 @@
         <v>6</v>
       </c>
       <c r="B43" t="str">
-        <v>Registry index maps (RIMs)</v>
+        <v>Registry index maps</v>
       </c>
       <c r="C43" t="str">
         <v>Number of Registry Index Maps (RIMs)</v>
@@ -77994,7 +78150,7 @@
         <v>11</v>
       </c>
       <c r="B62" t="str">
-        <v>Vulnerable persons identified</v>
+        <v>Vulnerable persons</v>
       </c>
       <c r="C62" t="str">
         <v>Number of Vulnerable Persons Identified for Social Safety Net Programs</v>
